--- a/files/SMS.xlsx
+++ b/files/SMS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Nome</t>
   </si>
@@ -28,25 +28,16 @@
     <t>Sobrenome</t>
   </si>
   <si>
-    <t>Maria</t>
-  </si>
-  <si>
-    <t>Pedro</t>
-  </si>
-  <si>
-    <t>81 8664-1979</t>
-  </si>
-  <si>
-    <t>Vinicius</t>
-  </si>
-  <si>
-    <t>Consultor</t>
-  </si>
-  <si>
-    <t>81 9791-2535</t>
-  </si>
-  <si>
     <t>Lista de contatos para envio de SMS</t>
+  </si>
+  <si>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>81 98895-2851</t>
   </si>
 </sst>
 </file>
@@ -90,10 +81,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -408,7 +398,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -429,24 +419,13 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C4" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
